--- a/data/trans_dic/P0902-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 13,09</t>
+          <t>5,67; 12,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,65</t>
+          <t>9,65; 17,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,0</t>
+          <t>7,3; 14,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,3</t>
+          <t>5,22; 11,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,33</t>
+          <t>9,54; 17,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,89; 32,78</t>
+          <t>21,79; 32,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 30,44</t>
+          <t>19,89; 30,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,36</t>
+          <t>8,8; 14,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,11</t>
+          <t>8,46; 14,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 23,84</t>
+          <t>16,86; 23,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 21,5</t>
+          <t>14,38; 20,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,76</t>
+          <t>7,6; 11,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,42</t>
+          <t>6,82; 12,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 14,19</t>
+          <t>8,14; 14,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,03</t>
+          <t>5,98; 10,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 21,02</t>
+          <t>13,49; 21,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 19,94</t>
+          <t>13,45; 20,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 22,06</t>
+          <t>15,18; 22,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 18,59</t>
+          <t>11,91; 18,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 27,45</t>
+          <t>21,52; 27,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,95</t>
+          <t>10,75; 15,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 16,83</t>
+          <t>12,43; 17,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,01</t>
+          <t>9,65; 13,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 23,44</t>
+          <t>18,28; 23,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,55</t>
+          <t>2,63; 7,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,03</t>
+          <t>8,11; 16,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,34</t>
+          <t>4,99; 10,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 17,22</t>
+          <t>10,31; 17,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 15,59</t>
+          <t>8,92; 15,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,75</t>
+          <t>13,5; 21,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 14,54</t>
+          <t>7,83; 15,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,28</t>
+          <t>14,51; 21,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,69</t>
+          <t>6,35; 10,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,71</t>
+          <t>12,08; 17,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,88</t>
+          <t>7,17; 11,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,02</t>
+          <t>13,19; 18,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,52</t>
+          <t>2,21; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 19,88</t>
+          <t>11,49; 19,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 20,67</t>
+          <t>12,99; 20,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 22,98</t>
+          <t>13,62; 22,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 18,28</t>
+          <t>10,96; 18,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,41; 36,98</t>
+          <t>27,43; 37,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,09; 34,85</t>
+          <t>25,38; 35,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 25,91</t>
+          <t>12,01; 26,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,24</t>
+          <t>7,08; 11,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 26,69</t>
+          <t>20,67; 26,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 26,81</t>
+          <t>20,21; 26,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 23,29</t>
+          <t>14,07; 22,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,77</t>
+          <t>4,48; 11,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,24</t>
+          <t>7,6; 16,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,07</t>
+          <t>4,66; 12,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,63</t>
+          <t>4,4; 10,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 16,56</t>
+          <t>7,56; 17,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 33,09</t>
+          <t>20,92; 33,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 18,43</t>
+          <t>9,85; 19,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,07</t>
+          <t>9,39; 15,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,62</t>
+          <t>7,07; 12,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 23,49</t>
+          <t>15,83; 23,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,2</t>
+          <t>8,26; 14,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,94</t>
+          <t>7,89; 11,8</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,66</t>
+          <t>5,32; 11,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,87</t>
+          <t>9,17; 17,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,07</t>
+          <t>10,25; 18,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 14,41</t>
+          <t>8,5; 14,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 21,33</t>
+          <t>12,37; 21,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 21,36</t>
+          <t>12,75; 21,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,69; 26,47</t>
+          <t>16,23; 26,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 18,73</t>
+          <t>12,66; 18,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,33</t>
+          <t>9,85; 15,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,07</t>
+          <t>11,96; 17,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,19</t>
+          <t>14,35; 21,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,54</t>
+          <t>11,21; 15,64</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,77</t>
+          <t>7,1; 12,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,52</t>
+          <t>5,41; 9,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,37</t>
+          <t>6,5; 11,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,28</t>
+          <t>9,91; 15,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 16,1</t>
+          <t>10,71; 16,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,17</t>
+          <t>12,48; 18,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 22,46</t>
+          <t>15,98; 22,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 22,06</t>
+          <t>7,29; 22,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 13,44</t>
+          <t>9,68; 13,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,36</t>
+          <t>9,58; 13,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,07; 16,03</t>
+          <t>11,99; 16,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,85; 17,71</t>
+          <t>8,88; 17,62</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,41</t>
+          <t>8,35; 12,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,21</t>
+          <t>8,33; 13,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,73</t>
+          <t>4,38; 7,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,33</t>
+          <t>3,88; 12,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,04</t>
+          <t>13,85; 19,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,83</t>
+          <t>14,54; 20,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 15,73</t>
+          <t>10,43; 15,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,88</t>
+          <t>17,8; 22,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,18</t>
+          <t>11,56; 15,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,38; 15,93</t>
+          <t>12,21; 15,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,25</t>
+          <t>7,99; 11,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 16,48</t>
+          <t>8,29; 16,72</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,22</t>
+          <t>7,28; 9,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,19</t>
+          <t>9,89; 12,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,28</t>
+          <t>8,36; 10,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,33</t>
+          <t>9,01; 13,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,84</t>
+          <t>13,38; 15,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,28</t>
+          <t>18,64; 21,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,5; 19,19</t>
+          <t>16,44; 19,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,78</t>
+          <t>14,74; 19,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,26</t>
+          <t>10,69; 12,26</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,61; 16,43</t>
+          <t>14,78; 16,42</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,44</t>
+          <t>12,75; 14,43</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,06; 16,21</t>
+          <t>13,25; 16,4</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15537; 35728</t>
+          <t>15489; 34225</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28337; 52026</t>
+          <t>28444; 52169</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21397; 44061</t>
+          <t>21432; 43882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15441; 35206</t>
+          <t>16271; 36069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24976; 47822</t>
+          <t>24894; 46886</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62864; 94164</t>
+          <t>62590; 94050</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56815; 87882</t>
+          <t>57436; 88202</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25481; 41585</t>
+          <t>25477; 41958</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45050; 75342</t>
+          <t>45187; 76249</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98947; 138724</t>
+          <t>98150; 138744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84431; 125228</t>
+          <t>83730; 122188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44635; 70673</t>
+          <t>45663; 71640</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34146; 61254</t>
+          <t>33609; 60462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39863; 71718</t>
+          <t>41155; 72335</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30977; 55438</t>
+          <t>30045; 53985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72125; 108983</t>
+          <t>69939; 109316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66889; 100470</t>
+          <t>67800; 101364</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79825; 115528</t>
+          <t>79516; 115519</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61109; 97222</t>
+          <t>62295; 96097</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109432; 141337</t>
+          <t>110831; 142507</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107259; 149020</t>
+          <t>107170; 151465</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122604; 173244</t>
+          <t>127964; 176749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99029; 143695</t>
+          <t>98972; 143151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>190781; 242220</t>
+          <t>188850; 237897</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9205; 24074</t>
+          <t>8385; 23745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27019; 51937</t>
+          <t>26291; 52210</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15626; 32948</t>
+          <t>15886; 33715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32141; 54412</t>
+          <t>32580; 55371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29242; 52302</t>
+          <t>29935; 53356</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45097; 74158</t>
+          <t>46021; 74177</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25055; 48901</t>
+          <t>26328; 51033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50271; 74165</t>
+          <t>50550; 73729</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42011; 69936</t>
+          <t>41521; 71883</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78700; 117761</t>
+          <t>80340; 117951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46942; 77816</t>
+          <t>46933; 77927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88935; 119772</t>
+          <t>87648; 119806</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8098; 23373</t>
+          <t>7920; 22217</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43106; 74340</t>
+          <t>42986; 72000</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47441; 76472</t>
+          <t>48045; 77266</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42759; 71709</t>
+          <t>42485; 71664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40510; 67914</t>
+          <t>40713; 67699</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106622; 143846</t>
+          <t>106686; 145118</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97170; 134966</t>
+          <t>98306; 137161</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58746; 123239</t>
+          <t>57137; 124893</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51389; 82094</t>
+          <t>51723; 82636</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157678; 203608</t>
+          <t>157680; 205541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151389; 203040</t>
+          <t>153066; 204401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108982; 183462</t>
+          <t>110833; 179810</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9014; 23930</t>
+          <t>9111; 23086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16300; 34520</t>
+          <t>16165; 34652</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9502; 25489</t>
+          <t>9852; 25475</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7845; 18942</t>
+          <t>7847; 18406</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15827; 34398</t>
+          <t>15705; 35625</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45744; 72657</t>
+          <t>45942; 72525</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20439; 40282</t>
+          <t>21524; 41589</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18971; 31291</t>
+          <t>19503; 31289</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27974; 51873</t>
+          <t>29063; 52423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68993; 101508</t>
+          <t>68416; 101424</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35252; 61025</t>
+          <t>35508; 62116</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29655; 46092</t>
+          <t>30447; 45528</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14466; 31584</t>
+          <t>14396; 31931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24635; 46218</t>
+          <t>25137; 46626</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27370; 50178</t>
+          <t>26974; 48942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21820; 38854</t>
+          <t>22906; 39183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34214; 59326</t>
+          <t>34419; 58784</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34321; 59828</t>
+          <t>35695; 61569</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42841; 72302</t>
+          <t>44337; 71913</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32266; 48155</t>
+          <t>32539; 48709</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>54275; 84177</t>
+          <t>54054; 83633</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64590; 100088</t>
+          <t>66232; 98721</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77380; 113609</t>
+          <t>76929; 114544</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58530; 81873</t>
+          <t>59017; 82387</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43554; 72363</t>
+          <t>43694; 74107</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35564; 63022</t>
+          <t>35819; 63078</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42857; 74666</t>
+          <t>42663; 72342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62288; 95132</t>
+          <t>61650; 96107</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68095; 102759</t>
+          <t>68342; 103740</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87431; 125756</t>
+          <t>86360; 127409</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>108621; 155281</t>
+          <t>110458; 155514</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>72311; 187306</t>
+          <t>61935; 189343</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>123108; 168490</t>
+          <t>121272; 163652</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128999; 180925</t>
+          <t>129634; 177902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162751; 215997</t>
+          <t>161652; 215603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>130272; 260616</t>
+          <t>130631; 259319</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>61776; 92301</t>
+          <t>62099; 93722</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>65534; 102914</t>
+          <t>64912; 101842</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33572; 60217</t>
+          <t>34125; 61410</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33282; 114480</t>
+          <t>36043; 114698</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>106390; 149148</t>
+          <t>108509; 152395</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119251; 162984</t>
+          <t>119509; 165906</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86454; 129966</t>
+          <t>86155; 127868</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128496; 164187</t>
+          <t>127786; 163507</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>181156; 231784</t>
+          <t>176582; 230336</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>198228; 254977</t>
+          <t>195451; 253294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130737; 180614</t>
+          <t>128206; 178774</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>132669; 271383</t>
+          <t>136551; 275235</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>238988; 302230</t>
+          <t>238484; 303784</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>341647; 417602</t>
+          <t>338801; 417786</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>281101; 349067</t>
+          <t>283906; 351962</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>321017; 460924</t>
+          <t>311360; 457551</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>451936; 535285</t>
+          <t>452227; 533460</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>665859; 756351</t>
+          <t>662615; 760522</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>584959; 680069</t>
+          <t>582595; 673586</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>528351; 724086</t>
+          <t>539522; 725184</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>713886; 816233</t>
+          <t>711231; 815883</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1019635; 1146997</t>
+          <t>1031353; 1146398</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>884783; 1002133</t>
+          <t>884720; 1001150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>929269; 1153476</t>
+          <t>943159; 1167569</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0902-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,54</t>
+          <t>5,69; 12,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,7</t>
+          <t>9,57; 17,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,94</t>
+          <t>7,26; 15,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 11,58</t>
+          <t>5,07; 10,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 17,98</t>
+          <t>9,67; 18,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 32,74</t>
+          <t>22,18; 33,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 30,55</t>
+          <t>19,62; 30,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,49</t>
+          <t>9,24; 15,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,28</t>
+          <t>8,42; 13,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 23,84</t>
+          <t>16,36; 23,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,98</t>
+          <t>14,32; 20,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 11,92</t>
+          <t>7,68; 11,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,26</t>
+          <t>6,83; 12,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,31</t>
+          <t>7,86; 14,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,74</t>
+          <t>6,08; 11,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 21,09</t>
+          <t>14,16; 21,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,11</t>
+          <t>13,36; 19,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 22,06</t>
+          <t>14,85; 22,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,37</t>
+          <t>11,92; 18,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 27,67</t>
+          <t>20,84; 27,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,19</t>
+          <t>10,89; 14,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,17</t>
+          <t>12,33; 16,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,96</t>
+          <t>9,78; 13,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,28; 23,02</t>
+          <t>18,38; 23,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,45</t>
+          <t>2,72; 7,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,11</t>
+          <t>8,41; 15,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,58</t>
+          <t>4,92; 10,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,52</t>
+          <t>10,07; 16,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 15,91</t>
+          <t>8,41; 15,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 21,75</t>
+          <t>13,08; 21,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,17</t>
+          <t>7,87; 14,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 21,16</t>
+          <t>14,29; 20,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,99</t>
+          <t>6,46; 10,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,74</t>
+          <t>11,63; 17,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,9</t>
+          <t>7,03; 11,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 18,03</t>
+          <t>12,94; 17,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,19</t>
+          <t>2,29; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,25</t>
+          <t>11,76; 19,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 20,88</t>
+          <t>13,01; 20,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 22,97</t>
+          <t>13,04; 22,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 18,23</t>
+          <t>11,19; 18,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,43; 37,31</t>
+          <t>27,5; 37,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,42</t>
+          <t>25,36; 35,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 26,25</t>
+          <t>21,05; 28,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,32</t>
+          <t>7,2; 11,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 26,94</t>
+          <t>20,74; 26,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 26,99</t>
+          <t>20,39; 26,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 22,83</t>
+          <t>18,46; 24,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,35</t>
+          <t>4,49; 11,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 16,3</t>
+          <t>7,83; 16,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,06</t>
+          <t>4,45; 12,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,33</t>
+          <t>4,32; 9,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 17,15</t>
+          <t>7,22; 16,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,92; 33,03</t>
+          <t>21,55; 33,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,03</t>
+          <t>9,4; 18,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,07</t>
+          <t>9,28; 14,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,76</t>
+          <t>6,67; 12,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 23,47</t>
+          <t>15,83; 23,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,45</t>
+          <t>8,29; 13,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,8</t>
+          <t>7,47; 11,19</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,79</t>
+          <t>5,58; 12,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,02</t>
+          <t>9,44; 17,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,25; 18,6</t>
+          <t>10,42; 18,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 14,53</t>
+          <t>8,06; 14,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 21,13</t>
+          <t>12,52; 21,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 21,99</t>
+          <t>12,4; 21,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,23; 26,33</t>
+          <t>16,46; 26,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,95</t>
+          <t>12,37; 18,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 15,23</t>
+          <t>9,91; 15,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 17,82</t>
+          <t>11,67; 17,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,35; 21,36</t>
+          <t>14,29; 21,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,21; 15,64</t>
+          <t>10,97; 15,34</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,05</t>
+          <t>7,0; 11,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,53</t>
+          <t>5,43; 9,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,02</t>
+          <t>6,49; 11,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 15,44</t>
+          <t>9,94; 14,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,71; 16,25</t>
+          <t>10,85; 16,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 18,41</t>
+          <t>12,47; 17,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,5</t>
+          <t>16,02; 22,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 22,29</t>
+          <t>19,8; 24,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 13,06</t>
+          <t>9,56; 13,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,14</t>
+          <t>9,34; 13,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 16,0</t>
+          <t>12,08; 15,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,88; 17,62</t>
+          <t>15,78; 19,32</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,6</t>
+          <t>8,12; 12,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,07</t>
+          <t>8,06; 13,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,89</t>
+          <t>4,41; 7,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,35</t>
+          <t>9,17; 13,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,85; 19,45</t>
+          <t>13,87; 19,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,54; 20,19</t>
+          <t>14,74; 20,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,48</t>
+          <t>10,04; 15,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,8; 22,78</t>
+          <t>17,26; 21,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 15,08</t>
+          <t>11,71; 15,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,82</t>
+          <t>12,25; 15,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,14</t>
+          <t>7,99; 11,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,72</t>
+          <t>13,91; 17,03</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,27</t>
+          <t>7,31; 9,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,2</t>
+          <t>9,89; 12,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,32; 10,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,24</t>
+          <t>11,4; 13,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,79</t>
+          <t>13,43; 15,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,4</t>
+          <t>18,55; 21,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,44; 19,0</t>
+          <t>16,32; 19,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,74; 19,81</t>
+          <t>18,61; 20,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,26</t>
+          <t>10,71; 12,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,78; 16,42</t>
+          <t>14,69; 16,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,43</t>
+          <t>12,64; 14,46</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,4</t>
+          <t>15,37; 16,99</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>60476</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15489; 34225</t>
+          <t>15526; 34462</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28444; 52169</t>
+          <t>28219; 52326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21432; 43882</t>
+          <t>21319; 44205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16271; 36069</t>
+          <t>16154; 33459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24894; 46886</t>
+          <t>25217; 47829</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62590; 94050</t>
+          <t>63711; 94898</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57436; 88202</t>
+          <t>56632; 87095</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25477; 41958</t>
+          <t>29213; 47689</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45187; 76249</t>
+          <t>44977; 74129</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98150; 138744</t>
+          <t>95187; 138487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83730; 122188</t>
+          <t>83424; 122195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45663; 71640</t>
+          <t>48758; 75005</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>93509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>125597</t>
+          <t>130655</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>214098</t>
+          <t>224165</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33609; 60462</t>
+          <t>33701; 60713</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41155; 72335</t>
+          <t>39724; 70933</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30045; 53985</t>
+          <t>30555; 56188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69939; 109316</t>
+          <t>75129; 114288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67800; 101364</t>
+          <t>67340; 98024</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79516; 115519</t>
+          <t>77762; 116622</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62295; 96097</t>
+          <t>62340; 98144</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110831; 142507</t>
+          <t>113884; 148607</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107170; 151465</t>
+          <t>108624; 149488</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127964; 176749</t>
+          <t>126911; 174317</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98972; 143151</t>
+          <t>100302; 140886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188850; 237897</t>
+          <t>198024; 252351</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61508</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>103701</t>
+          <t>102157</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8385; 23745</t>
+          <t>8663; 24947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26291; 52210</t>
+          <t>27252; 51327</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15886; 33715</t>
+          <t>15689; 34401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32580; 55371</t>
+          <t>31821; 53032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29935; 53356</t>
+          <t>28220; 53610</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46021; 74177</t>
+          <t>44614; 74320</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26328; 51033</t>
+          <t>26453; 50261</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50550; 73729</t>
+          <t>50844; 72166</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41521; 71883</t>
+          <t>42241; 69690</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80340; 117951</t>
+          <t>77376; 115898</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46933; 77927</t>
+          <t>46028; 78304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87648; 119806</t>
+          <t>86952; 117411</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>62945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>104992</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>151642</t>
+          <t>167938</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7920; 22217</t>
+          <t>8196; 22970</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42986; 72000</t>
+          <t>43982; 72795</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48045; 77266</t>
+          <t>48128; 77270</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42485; 71664</t>
+          <t>48583; 82404</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40713; 67699</t>
+          <t>41562; 68254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106686; 145118</t>
+          <t>106960; 144691</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98306; 137161</t>
+          <t>98233; 137612</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57137; 124893</t>
+          <t>88839; 121358</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51723; 82636</t>
+          <t>52570; 83886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157680; 205541</t>
+          <t>158249; 204306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>153066; 204401</t>
+          <t>154390; 202608</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>110833; 179810</t>
+          <t>146645; 193633</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>39749</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9111; 23086</t>
+          <t>9123; 23301</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16165; 34652</t>
+          <t>16648; 35441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9852; 25475</t>
+          <t>9400; 25433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7847; 18406</t>
+          <t>8860; 20119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15705; 35625</t>
+          <t>14991; 34748</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45942; 72525</t>
+          <t>47330; 72787</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21524; 41589</t>
+          <t>20550; 40273</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19503; 31289</t>
+          <t>20995; 33553</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29063; 52423</t>
+          <t>27407; 50563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68416; 101424</t>
+          <t>68431; 100390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35508; 62116</t>
+          <t>35612; 59972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30447; 45528</t>
+          <t>32224; 48249</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>70014</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14396; 31931</t>
+          <t>15110; 32781</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25137; 46626</t>
+          <t>25877; 47479</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26974; 48942</t>
+          <t>27420; 49358</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22906; 39183</t>
+          <t>21814; 38186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34419; 58784</t>
+          <t>34828; 59063</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35695; 61569</t>
+          <t>34722; 59377</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44337; 71913</t>
+          <t>44966; 72783</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32539; 48709</t>
+          <t>32626; 49459</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>54054; 83633</t>
+          <t>54416; 85584</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66232; 98721</t>
+          <t>64647; 99418</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76929; 114544</t>
+          <t>76609; 113931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59017; 82387</t>
+          <t>58606; 81976</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>87691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>138579</t>
+          <t>171725</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>216037</t>
+          <t>259416</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43694; 74107</t>
+          <t>43060; 72781</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35819; 63078</t>
+          <t>35926; 63298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42663; 72342</t>
+          <t>42643; 73258</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61650; 96107</t>
+          <t>71305; 107601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68342; 103740</t>
+          <t>69246; 102220</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86360; 127409</t>
+          <t>86296; 123374</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>110458; 155514</t>
+          <t>110746; 154352</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>61935; 189343</t>
+          <t>152868; 192138</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>121272; 163652</t>
+          <t>119755; 163588</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>129634; 177902</t>
+          <t>126445; 178885</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161652; 215603</t>
+          <t>162764; 215583</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>130631; 259319</t>
+          <t>235047; 287773</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78915</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>161537</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>223691</t>
+          <t>250451</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>62099; 93722</t>
+          <t>60407; 92175</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>64912; 101842</t>
+          <t>62825; 101466</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34125; 61410</t>
+          <t>34333; 60401</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36043; 114698</t>
+          <t>73193; 109311</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>108509; 152395</t>
+          <t>108710; 151183</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119509; 165906</t>
+          <t>121169; 164571</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86155; 127868</t>
+          <t>82950; 126591</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>127786; 163507</t>
+          <t>143475; 181644</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>176582; 230336</t>
+          <t>178885; 231682</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>195451; 253294</t>
+          <t>196037; 253415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128206; 178774</t>
+          <t>128225; 178636</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>136551; 275235</t>
+          <t>226634; 277461</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>238484; 303784</t>
+          <t>239433; 300171</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>338801; 417786</t>
+          <t>338802; 417195</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>283906; 351962</t>
+          <t>282523; 350229</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>311360; 457551</t>
+          <t>402461; 481057</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>452227; 533460</t>
+          <t>453785; 535608</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>662615; 760522</t>
+          <t>659330; 755598</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>582595; 673586</t>
+          <t>578553; 679771</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>539522; 725184</t>
+          <t>694929; 774617</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>711231; 815883</t>
+          <t>712708; 815514</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1031353; 1146398</t>
+          <t>1025490; 1146875</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>884720; 1001150</t>
+          <t>877351; 1003038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>943159; 1167569</t>
+          <t>1116300; 1233820</t>
         </is>
       </c>
     </row>
